--- a/public/Add_Users_Template.xlsx
+++ b/public/Add_Users_Template.xlsx
@@ -1,52 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,102 +445,222 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col width="12.796875" customWidth="1" min="1" max="4"/>
+    <col width="15.796875" customWidth="1" min="5" max="5"/>
+    <col width="14.796875" customWidth="1" min="6" max="6"/>
+    <col width="17.796875" customWidth="1" min="7" max="7"/>
+    <col width="15.796875" customWidth="1" min="8" max="8"/>
+    <col width="12.796875" customWidth="1" min="9" max="10"/>
+    <col width="15.796875" customWidth="1" min="11" max="11"/>
+    <col width="12.796875" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
+    <row r="1" ht="15.6" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>คำนำหน้า</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ชื่อ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>นามสกุล</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>อีเมล</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>เบอร์ติดต่อ</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ตำแหน่งงาน</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>เลขที่ตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>วันที่บรรจุ</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>สายงาน</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>สาขา</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ประเภทบุคคล</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>บทบาท</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.6" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$A$1:$A$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$B$1:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$C$1:$C$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$D$1:$D$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>คำนำหน้า</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ชื่อ</v>
-      </c>
-      <c r="C1" t="str">
-        <v>นามสกุล</v>
-      </c>
-      <c r="D1" t="str">
-        <v>อีเมล</v>
-      </c>
-      <c r="E1" t="str">
-        <v>เบอร์ติดต่อ</v>
-      </c>
-      <c r="F1" t="str">
-        <v>ตำแหน่งงาน</v>
-      </c>
-      <c r="G1" t="str">
-        <v>เลขที่ตำแหน่ง</v>
-      </c>
-      <c r="H1" t="str">
-        <v>วันที่บรรจุ</v>
-      </c>
-      <c r="I1" t="str">
-        <v>สายงาน</v>
-      </c>
-      <c r="J1" t="str">
-        <v>สาขา</v>
-      </c>
-      <c r="K1" t="str">
-        <v>ประเภทบุคคล</v>
-      </c>
-      <c r="L1" t="str">
-        <v>บทบาท</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>สายสนับสนุน</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ข้าราชการพลเรือนในสถาบันอุดมศึกษา</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>USER</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>นาย</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>นาย</v>
-      </c>
-      <c r="B2" t="str">
-        <v>สมชาย</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ใจดี</v>
-      </c>
-      <c r="D2" t="str">
-        <v>somchai@rmuti.ac.th</v>
-      </c>
-      <c r="E2" t="str">
-        <v>0812345678</v>
-      </c>
-      <c r="F2" t="str">
-        <v>อาจารย์</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ENG-001</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2023-06-01</v>
-      </c>
-      <c r="I2" t="str">
-        <v>สายวิชาการ</v>
-      </c>
-      <c r="J2" t="str">
-        <v>วิศวกรรมคอมพิวเตอร์</v>
-      </c>
-      <c r="K2" t="str">
-        <v>ข้าราชการ</v>
-      </c>
-      <c r="L2" t="str">
-        <v>USER</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>สายวิชาการ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ลูกจ้างประจำ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADMIN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>นาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>พนักงานราชการ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>APPROVER_1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>นางสาว</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>พนักงานในสถาบันอุดมศึกษา</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>APPROVER_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ลูกจ้างเงินรายได้</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>APPROVER_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>APPROVER_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>APPROVER_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/Add_Users_Template.xlsx
+++ b/public/Add_Users_Template.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.796875" customWidth="1" min="1" max="4"/>
@@ -466,62 +466,137 @@
     <row r="1" ht="15.6" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>คำนำหน้า</t>
+          <t xml:space="preserve">คำนำหน้า</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ชื่อ</t>
+          <t xml:space="preserve">ชื่อ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>นามสกุล</t>
+          <t xml:space="preserve">นามสกุล</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>อีเมล</t>
+          <t xml:space="preserve">อีเมล</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>เบอร์ติดต่อ</t>
+          <t xml:space="preserve">เบอร์ติดต่อ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ตำแหน่งงาน</t>
+          <t xml:space="preserve">ตำแหน่งงาน</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>เลขที่ตำแหน่ง</t>
+          <t xml:space="preserve">เลขที่ตำแหน่ง</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>วันที่บรรจุ</t>
+          <t xml:space="preserve">วันที่บรรจุ</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>สายงาน</t>
+          <t xml:space="preserve">สายงาน</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>สาขา</t>
+          <t xml:space="preserve">สาขา</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ประเภทบุคคล</t>
+          <t xml:space="preserve">ประเภทบุคคล</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>บทบาท</t>
+          <t xml:space="preserve">บทบาท</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาป่วย (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาคลอดบุตร (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลากิจส่วนตัว (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาพักผ่อน (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาอุปสมบท (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาตรวจเลือก/เตรียมพล (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาไปศึกษา (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาช่วยเหลือภริยาที่คลอดบุตร (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาฟื้นฟูสมรรถภาพด้านอาชีพ (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาถือศีล/ปฏิบัติธรรม สตรี (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาองค์การระหว่างประเทศ (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาติดตามคู่สมรส (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาประกอบพิธีฮัจย์ (วันที่ใช้ไปแล้ว)</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ลาฝึกอบรม/วิจัย/ดูงาน (วันคงเหลือ)</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ไปราชการ (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
     </row>

--- a/public/Add_Users_Template.xlsx
+++ b/public/Add_Users_Template.xlsx
@@ -466,143 +466,143 @@
     <row r="1" ht="15.6" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">คำนำหน้า</t>
+          <t>คำนำหน้า</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อ</t>
+          <t>ชื่อ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">นามสกุล</t>
+          <t>นามสกุล</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">อีเมล</t>
+          <t>อีเมล</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">เบอร์ติดต่อ</t>
+          <t>เบอร์ติดต่อ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตำแหน่งงาน</t>
+          <t>ตำแหน่งงาน</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">เลขที่ตำแหน่ง</t>
+          <t>เลขที่ตำแหน่ง</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่บรรจุ</t>
+          <t>วันที่บรรจุ</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">สายงาน</t>
+          <t>สายงาน</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">สาขา</t>
+          <t>สาขา</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประเภทบุคคล</t>
+          <t>ประเภทบุคคล</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t xml:space="preserve">บทบาท</t>
+          <t>บทบาท</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาป่วย (วันคงเหลือ)</t>
+          <t>ลาป่วย (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาคลอดบุตร (วันคงเหลือ)</t>
+          <t>ลาคลอดบุตร (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลากิจส่วนตัว (วันคงเหลือ)</t>
+          <t>ลากิจส่วนตัว (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาพักผ่อน (วันคงเหลือ)</t>
+          <t>ลาพักผ่อน (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาอุปสมบท (วันที่ใช้ไปแล้ว)</t>
+          <t>ลาอุปสมบท (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาตรวจเลือก/เตรียมพล (วันที่ใช้ไปแล้ว)</t>
+          <t>ลาตรวจเลือก/เตรียมพล (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาไปศึกษา (วันคงเหลือ)</t>
+          <t>ลาไปศึกษา (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาช่วยเหลือภริยาที่คลอดบุตร (วันคงเหลือ)</t>
+          <t>ลาช่วยเหลือภริยาที่คลอดบุตร (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาฟื้นฟูสมรรถภาพด้านอาชีพ (วันคงเหลือ)</t>
+          <t>ลาฟื้นฟูสมรรถภาพด้านอาชีพ (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาถือศีล/ปฏิบัติธรรม สตรี (วันที่ใช้ไปแล้ว)</t>
+          <t>ลาถือศีล/ปฏิบัติธรรม สตรี (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาองค์การระหว่างประเทศ (วันที่ใช้ไปแล้ว)</t>
+          <t>ลาองค์การระหว่างประเทศ (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาติดตามคู่สมรส (วันคงเหลือ)</t>
+          <t>ลาติดตามคู่สมรส (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาประกอบพิธีฮัจย์ (วันที่ใช้ไปแล้ว)</t>
+          <t>ลาประกอบพิธีฮัจย์ (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลาฝึกอบรม/วิจัย/ดูงาน (วันคงเหลือ)</t>
+          <t>ลาฝึกอบรม/วิจัย/ดูงาน (วันคงเหลือ)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ไปราชการ (วันที่ใช้ไปแล้ว)</t>
+          <t>ไปราชการ (วันที่ใช้ไปแล้ว)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.6" customHeight="1"/>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="8">
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Lists!$A$1:$A$2</formula1>
     </dataValidation>
@@ -612,8 +612,20 @@
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Lists!$C$1:$C$8</formula1>
     </dataValidation>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Lists!$D$1:$D$3</formula1>
+    </dataValidation>
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$D$1:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$A$1:$A$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$B$1:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$C$1:$C$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
